--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 10/02. Trả bảo hành/TBH_NgocHoan_011026.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 10/02. Trả bảo hành/TBH_NgocHoan_011026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 10\02. Trả bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B653F22-172A-40B3-A0C6-97EA78C035D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997F9759-EE2F-44C7-A480-4A7B85CD6976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -506,6 +506,39 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -523,39 +556,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1056,69 +1056,69 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="47"/>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="48" t="s">
+      <c r="A1" s="41"/>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
+      <c r="E1" s="42"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47"/>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="49" t="s">
+      <c r="A2" s="41"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="51"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="45"/>
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="47"/>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="52" t="s">
+      <c r="A3" s="41"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="54"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="48"/>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="47"/>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="55" t="s">
+      <c r="A4" s="41"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="56"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="56"/>
-      <c r="H4" s="56"/>
-      <c r="I4" s="57"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="51"/>
     </row>
     <row r="5" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="24" t="s">
@@ -1264,34 +1264,34 @@
       <c r="I13" s="9"/>
     </row>
     <row r="14" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="44"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="44"/>
-      <c r="E14" s="44"/>
+      <c r="B14" s="55"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="55"/>
       <c r="F14" s="26"/>
-      <c r="G14" s="46" t="s">
+      <c r="G14" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
     </row>
     <row r="15" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
       <c r="F15" s="40"/>
-      <c r="G15" s="45" t="s">
+      <c r="G15" s="56" t="s">
         <v>13</v>
       </c>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
     </row>
     <row r="16" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="27"/>
@@ -1338,19 +1338,19 @@
       <c r="I19" s="16"/>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="44" t="s">
+      <c r="A20" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
-      <c r="D20" s="44"/>
-      <c r="E20" s="44"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="55"/>
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
       <c r="F20" s="14"/>
-      <c r="G20" s="44" t="s">
+      <c r="G20" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="44"/>
-      <c r="I20" s="44"/>
+      <c r="H20" s="55"/>
+      <c r="I20" s="55"/>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="7"/>
@@ -1364,17 +1364,12 @@
       <c r="I21" s="7"/>
     </row>
     <row r="23" spans="1:9" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="B23" s="43"/>
-      <c r="C23" s="43"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
     </row>
     <row r="62" ht="20.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="A14:E14"/>
@@ -1383,6 +1378,11 @@
     <mergeCell ref="G14:I14"/>
     <mergeCell ref="G15:I15"/>
     <mergeCell ref="G20:I20"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -1399,18 +1399,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="46" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
       <c r="I1" s="26"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1473,18 +1473,18 @@
       <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
-      <c r="E7" s="44" t="s">
+      <c r="B7" s="55"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="55"/>
+      <c r="E7" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="44"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="44"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
       <c r="I7" s="14"/>
     </row>
   </sheetData>
